--- a/sampleprojects/CorporateTax/excel/states/NM_corp.xlsx
+++ b/sampleprojects/CorporateTax/excel/states/NM_corp.xlsx
@@ -193,13 +193,13 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>apportionment</t>
+    <t>nm_apportionment</t>
   </si>
   <si>
     <t>(3 attributes)</t>
   </si>
   <si>
-    <t>nm_economic_nexus_threshold</t>
+    <t>economic_nexus_threshold</t>
   </si>
   <si>
     <t>double</t>
@@ -214,7 +214,7 @@
     <t>NM economic nexus gross receipts threshold: $100,000</t>
   </si>
   <si>
-    <t>nm_state_tax_rate</t>
+    <t>state_tax_rate</t>
   </si>
   <si>
     <t>0.059</t>
@@ -223,7 +223,7 @@
     <t>NM corporate income tax rate: 5.9% flat rate (NMSA § 7-2A-5, effective 2025)</t>
   </si>
   <si>
-    <t>nm_transaction_threshold</t>
+    <t>transaction_threshold</t>
   </si>
   <si>
     <t>integer</t>
